--- a/reports/一级子公司B_利润表_2026-02.xlsx
+++ b/reports/一级子公司B_利润表_2026-02.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>43353282</v>
+        <v>57865912</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>0</v>
+        <v>12878625</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>0</v>
+        <v>25713990</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>0</v>
+        <v>181937</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>0</v>
+        <v>364302</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>0</v>
+        <v>163372</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>0</v>
+        <v>327384</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>0</v>
+        <v>135801</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>0</v>
+        <v>272255</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>0</v>
+        <v>126454</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>0</v>
+        <v>253522</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0</v>
+        <v>72136</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>0</v>
+        <v>144564</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>0</v>
+        <v>54060</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>0</v>
+        <v>108255</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>43353282</v>
+        <v>57132152</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0</v>
+        <v>12144865</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0</v>
+        <v>7233878</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>0</v>
+        <v>14443705</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>0</v>
+        <v>1087766</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>0</v>
+        <v>2170614</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0</v>
+        <v>545217</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>0</v>
+        <v>1087753</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>0</v>
+        <v>3642063</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>0</v>
+        <v>7267915</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>0</v>
+        <v>364645</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>0</v>
+        <v>728120</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>0</v>
+        <v>273537</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>0</v>
+        <v>546690</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>0</v>
+        <v>455510</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>0</v>
+        <v>911315</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>0</v>
+        <v>363775</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>0</v>
+        <v>728492</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>43271014</v>
+        <v>43551375</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>86771971</v>
+        <v>87280582</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>82268</v>
+        <v>82276</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>165157</v>
+        <v>164953</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>812701</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>1629297</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>540935</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>1083964</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>40054155</v>
+        <v>51636136</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>22704831</v>
+        <v>29111625</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>136646</v>
+        <v>6498658</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>271925</v>
+        <v>12985634</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>22568185</v>
+        <v>22612967</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>45173567</v>
+        <v>45146245</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1360166</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>2714044</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>436305</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>870470</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>273213</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>545244</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>328209</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>655435</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>246170</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>492060</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>163953</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>328057</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>136377</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>273138</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1082019</v>
+        <v>1088421</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>2174956</v>
+        <v>2181449</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>36394</v>
+        <v>36190</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>72748</v>
+        <v>72557</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>2274889</v>
+        <v>2256918</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>4527887</v>
+        <v>4524483</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>13526194</v>
+        <v>13521404</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>27111794</v>
+        <v>27092730</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>0</v>
+        <v>2252404</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>0</v>
+        <v>4509338</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>466222</v>
+        <v>460971</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>929143</v>
+        <v>921930</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>412093</v>
+        <v>410371</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>821796</v>
+        <v>819899</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>30716</v>
+        <v>30846</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>61712</v>
+        <v>61577</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>139155</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>277654</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>238674</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>476184</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>93159</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>185928</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>69936</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>139678</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>116549</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>232997</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>341501</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>683408</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>61971</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>124131</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>46366</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>92935</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>77085</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>154550</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>53845</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>107939</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>38408</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>76951</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>30715</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>61484</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>23052</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>3299127</v>
+        <v>6369862</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>-90772</v>
+        <v>4101536</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>136108</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>271565</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>38757</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>77326</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>61429</v>
+        <v>62117</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>123388</v>
+        <v>123984</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>3237698</v>
+        <v>6443853</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>1864392</v>
+        <v>1864622</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>3710562</v>
+        <v>3728133</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>1373306</v>
+        <v>4579231</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>1373306</v>
+        <v>4579231</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>1373306</v>
+        <v>4579231</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>1373306</v>
+        <v>4579231</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>1373306</v>
+        <v>4579231</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
